--- a/education_surveys/017_hieroglyph_selection_survey--education_surveys.xlsx
+++ b/education_surveys/017_hieroglyph_selection_survey--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -1374,24 +1374,24 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>User_Symbols</t>
+          <t>User symbols</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>egyptian_symbols_choices</t>
+          <t>preferences_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>user_symbols</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>User_symbols</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>d</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
     </row>
@@ -1454,29 +1454,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>e</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>preferences_choices</t>
+          <t>education_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>Primary</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Primary</t>
+          <t>Secondary</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>secondary</t>
+          <t>university</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Secondary</t>
+          <t>University</t>
         </is>
       </c>
     </row>
@@ -1522,29 +1522,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>University</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>education_choices</t>
+          <t>time_spent_on_hobby_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1607,29 +1607,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>time_spent_on_hobby_choices</t>
+          <t>age_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20-30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20-30</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20-30</t>
+          <t>31-40</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>20-30</t>
+          <t>31-40</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>31-40</t>
+          <t>41-50</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>31-40</t>
+          <t>41-50</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>41-50</t>
+          <t>51-60</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>41-50</t>
+          <t>51-60</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>51-60</t>
+          <t>61-70</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>51-60</t>
+          <t>61-70</t>
         </is>
       </c>
     </row>
@@ -1709,29 +1709,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>61-70</t>
+          <t>over_70</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>61-70</t>
+          <t>Over 70</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>age_choices</t>
+          <t>income_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>over_70</t>
+          <t>0-10000</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Over 70</t>
+          <t>0-10000</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0-10000</t>
+          <t>10001-50000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0-10000</t>
+          <t>10001-50000</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10001-50000</t>
+          <t>50001-100000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>10001-50000</t>
+          <t>50001-100000</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>50001-100000</t>
+          <t>100001-200000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>50001-100000</t>
+          <t>100001-200000</t>
         </is>
       </c>
     </row>
@@ -1794,27 +1794,10 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>100001-200000</t>
+          <t>200001-300000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
-        <is>
-          <t>100001-200000</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>income_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>200001-300000</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
         <is>
           <t>200001-300000</t>
         </is>
